--- a/data/00406A_20260826.xlsx
+++ b/data/00406A_20260826.xlsx
@@ -34,16 +34,16 @@
     <x:t>基金每單位淨值(台幣)</x:t>
   </x:si>
   <x:si>
-    <x:t>2026/08/25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26,073,228,532</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,766,062,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.43</x:t>
+    <x:t>2026/08/26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,880,196,023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,788,562,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.64</x:t>
   </x:si>
   <x:si>
     <x:t>序號</x:t>
@@ -76,7 +76,7 @@
     <x:t>991,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>9.09</x:t>
+    <x:t>8.89</x:t>
   </x:si>
   <x:si>
     <x:t>2383</x:t>
@@ -91,7 +91,7 @@
     <x:t>265,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>5.69</x:t>
+    <x:t>5.81</x:t>
   </x:si>
   <x:si>
     <x:t>2454</x:t>
@@ -106,7 +106,7 @@
     <x:t>325,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.66</x:t>
+    <x:t>4.77</x:t>
   </x:si>
   <x:si>
     <x:t>2059</x:t>
@@ -121,7 +121,7 @@
     <x:t>80,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.38</x:t>
+    <x:t>4.32</x:t>
   </x:si>
   <x:si>
     <x:t>3017</x:t>
@@ -136,7 +136,7 @@
     <x:t>362,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.10</x:t>
+    <x:t>4.25</x:t>
   </x:si>
   <x:si>
     <x:t>3037</x:t>
@@ -151,7 +151,22 @@
     <x:t>966,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.06</x:t>
+    <x:t>4.17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智邦科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Accton Technology Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>530,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.05</x:t>
   </x:si>
   <x:si>
     <x:t>6223</x:t>
@@ -163,25 +178,10 @@
     <x:t>MPI Corporation</x:t>
   </x:si>
   <x:si>
-    <x:t>184,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>智邦科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Accton Technology Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>493,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.84</x:t>
+    <x:t>204,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.82</x:t>
   </x:si>
   <x:si>
     <x:t>3653</x:t>
@@ -196,7 +196,22 @@
     <x:t>151,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>3.01</x:t>
+    <x:t>3.22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>創意電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Global Unichip Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.10</x:t>
   </x:si>
   <x:si>
     <x:t>6669</x:t>
@@ -211,22 +226,7 @@
     <x:t>119,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3443</x:t>
-  </x:si>
-  <x:si>
-    <x:t>創意電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Global Unichip Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.91</x:t>
+    <x:t>3.00</x:t>
   </x:si>
   <x:si>
     <x:t>2308</x:t>
@@ -238,10 +238,10 @@
     <x:t>Delta Electronics, Inc.</x:t>
   </x:si>
   <x:si>
-    <x:t>396,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.60</x:t>
+    <x:t>413,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.69</x:t>
   </x:si>
   <x:si>
     <x:t>8046</x:t>
@@ -256,7 +256,7 @@
     <x:t>510,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.27</x:t>
+    <x:t>2.24</x:t>
   </x:si>
   <x:si>
     <x:t>5274</x:t>
@@ -271,7 +271,7 @@
     <x:t>37,800.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.23</x:t>
+    <x:t>2.21</x:t>
   </x:si>
   <x:si>
     <x:t>3665</x:t>
@@ -286,7 +286,7 @@
     <x:t>264,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.10</x:t>
+    <x:t>1.97</x:t>
   </x:si>
   <x:si>
     <x:t>6274</x:t>
@@ -301,7 +301,7 @@
     <x:t>338,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.93</x:t>
+    <x:t>1.92</x:t>
   </x:si>
   <x:si>
     <x:t>7769</x:t>
@@ -316,7 +316,22 @@
     <x:t>77,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.83</x:t>
+    <x:t>1.81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>國巨*</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yageo Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>712,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.42</x:t>
   </x:si>
   <x:si>
     <x:t>3711</x:t>
@@ -331,7 +346,22 @@
     <x:t>626,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.42</x:t>
+    <x:t>1.38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>金像電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold Circuit Electronics Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.28</x:t>
   </x:si>
   <x:si>
     <x:t>2303</x:t>
@@ -346,7 +376,7 @@
     <x:t>2,650,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.27</x:t>
+    <x:t>1.22</x:t>
   </x:si>
   <x:si>
     <x:t>2360</x:t>
@@ -361,22 +391,7 @@
     <x:t>164,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2368</x:t>
-  </x:si>
-  <x:si>
-    <x:t>金像電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold Circuit Electronics Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>331,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.23</x:t>
+    <x:t>1.21</x:t>
   </x:si>
   <x:si>
     <x:t>3008</x:t>
@@ -391,7 +406,37 @@
     <x:t>40,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.88</x:t>
+    <x:t>0.94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>萬潤科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>All Ring Tech Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>一詮精密工業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I-Chiun Precision Ind. Co.,Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>837,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.82</x:t>
   </x:si>
   <x:si>
     <x:t>6488</x:t>
@@ -406,51 +451,6 @@
     <x:t>228,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>萬潤科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>All Ring Tech Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>172,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2486</x:t>
-  </x:si>
-  <x:si>
-    <x:t>一詮精密工業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I-Chiun Precision Ind. Co.,Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>837,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>國巨*</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yageo Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>382,000.00</x:t>
-  </x:si>
-  <x:si>
     <x:t>0.80</x:t>
   </x:si>
   <x:si>
@@ -466,7 +466,34 @@
     <x:t>152,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.71</x:t>
+    <x:t>0.68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>景碩科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kinsus Interconnect Technology</x:t>
+  </x:si>
+  <x:si>
+    <x:t>208,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>聯鈞光電</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elite Advanced Laser Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>315,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.67</x:t>
   </x:si>
   <x:si>
     <x:t>2344</x:t>
@@ -481,34 +508,7 @@
     <x:t>973,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>景碩科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kinsus Interconnect Technology</x:t>
-  </x:si>
-  <x:si>
-    <x:t>208,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3450</x:t>
-  </x:si>
-  <x:si>
-    <x:t>聯鈞光電</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elite Advanced Laser Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>315,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.64</x:t>
+    <x:t>0.66</x:t>
   </x:si>
   <x:si>
     <x:t>3081</x:t>
@@ -523,7 +523,22 @@
     <x:t>52,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.59</x:t>
+    <x:t>0.63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台灣化學纖維</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Formosa Chemicals &amp; Fiber Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,500,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.56</x:t>
   </x:si>
   <x:si>
     <x:t>6515</x:t>
@@ -538,22 +553,7 @@
     <x:t>24,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台灣化學纖維</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Formosa Chemicals &amp; Fiber Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,500,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.56</x:t>
+    <x:t>0.54</x:t>
   </x:si>
   <x:si>
     <x:t>6510</x:t>
@@ -568,7 +568,7 @@
     <x:t>45,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.46</x:t>
+    <x:t>0.44</x:t>
   </x:si>
   <x:si>
     <x:t>2886</x:t>
@@ -580,7 +580,7 @@
     <x:t>Mega Financial Holding Co.,Ltd</x:t>
   </x:si>
   <x:si>
-    <x:t>0.45</x:t>
+    <x:t>0.43</x:t>
   </x:si>
   <x:si>
     <x:t>2885</x:t>
@@ -595,7 +595,22 @@
     <x:t>1,788,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.43</x:t>
+    <x:t>0.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>大量科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ta Liang Technology Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.40</x:t>
   </x:si>
   <x:si>
     <x:t>4958</x:t>
@@ -637,31 +652,64 @@
     <x:t>44,000.00</x:t>
   </x:si>
   <x:si>
+    <x:t>0.33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105</x:t>
+  </x:si>
+  <x:si>
+    <x:t>穩懋半導體</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Win Semiconductors Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>216,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>研華</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Advantech Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121,000.00</x:t>
+  </x:si>
+  <x:si>
     <x:t>0.31</x:t>
   </x:si>
   <x:si>
-    <x:t>2395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>研華</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Advantech Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>121,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3105</x:t>
-  </x:si>
-  <x:si>
-    <x:t>穩懋半導體</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Win Semiconductors Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>216,000.00</x:t>
+    <x:t>1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>南亞塑膠工業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nan Ya Plastics Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>395,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>啟碁科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wistron NeWeb Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>323,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.29</x:t>
   </x:si>
   <x:si>
     <x:t>3260</x:t>
@@ -676,43 +724,7 @@
     <x:t>180,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>大量科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ta Liang Technology Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>南亞塑膠工業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nan Ya Plastics Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>395,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6285</x:t>
-  </x:si>
-  <x:si>
-    <x:t>啟碁科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wistron NeWeb Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>323,000.00</x:t>
+    <x:t>0.28</x:t>
   </x:si>
   <x:si>
     <x:t>6531</x:t>
@@ -769,9 +781,33 @@
     <x:t>110,000.00</x:t>
   </x:si>
   <x:si>
+    <x:t>0.24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>辛耘企業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scientech Corporation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78,000.00</x:t>
+  </x:si>
+  <x:si>
     <x:t>0.22</x:t>
   </x:si>
   <x:si>
+    <x:t>3131</x:t>
+  </x:si>
+  <x:si>
+    <x:t>弘塑科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Process Technology Corp.</x:t>
+  </x:si>
+  <x:si>
     <x:t>6139</x:t>
   </x:si>
   <x:si>
@@ -787,27 +823,6 @@
     <x:t>0.21</x:t>
   </x:si>
   <x:si>
-    <x:t>3583</x:t>
-  </x:si>
-  <x:si>
-    <x:t>辛耘企業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scientech Corporation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3131</x:t>
-  </x:si>
-  <x:si>
-    <x:t>弘塑科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grand Process Technology Corp.</x:t>
-  </x:si>
-  <x:si>
     <x:t>2449</x:t>
   </x:si>
   <x:si>
@@ -910,13 +925,13 @@
     <x:t>臺股期貨</x:t>
   </x:si>
   <x:si>
-    <x:t>650.00</x:t>
+    <x:t>660.00</x:t>
   </x:si>
   <x:si>
     <x:t>202609</x:t>
   </x:si>
   <x:si>
-    <x:t>22.45</x:t>
+    <x:t>22.59</x:t>
   </x:si>
   <x:si>
     <x:t>商品代碼</x:t>
@@ -928,34 +943,34 @@
     <x:t>商品名稱</x:t>
   </x:si>
   <x:si>
+    <x:t>TX1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>臺指選擇權第一週週三到期契約</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-900.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-5.72</x:t>
+  </x:si>
+  <x:si>
     <x:t>TXY</x:t>
   </x:si>
   <x:si>
-    <x:t>C</x:t>
-  </x:si>
-  <x:si>
     <x:t>臺指選擇權第四週週五到期契約</x:t>
   </x:si>
   <x:si>
-    <x:t>-770.00</x:t>
+    <x:t>-2,100.00</x:t>
   </x:si>
   <x:si>
     <x:t>202608</x:t>
   </x:si>
   <x:si>
-    <x:t>-5.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>臺指選擇權第四週週三到期契約</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-2,530.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-16.30</x:t>
+    <x:t>-15.56</x:t>
   </x:si>
   <x:si>
     <x:t>項目</x:t>
@@ -973,25 +988,25 @@
     <x:t>TWD</x:t>
   </x:si>
   <x:si>
-    <x:t>5,104,944,940.00 (TWD)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.58</x:t>
+    <x:t>4,141,931,856.00 (TWD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.41</x:t>
   </x:si>
   <x:si>
     <x:t>保證金</x:t>
   </x:si>
   <x:si>
-    <x:t>2,266,276,749.00 (TWD)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.69</x:t>
+    <x:t>2,331,342,288.00 (TWD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.67</x:t>
   </x:si>
   <x:si>
     <x:t>應收(付)證券款</x:t>
   </x:si>
   <x:si>
-    <x:t>-2,296,925,861.00 (TWD)</x:t>
+    <x:t>-1,722,781,628.00 (TWD)</x:t>
   </x:si>
   <x:si>
     <x:t>0.00</x:t>
@@ -2051,7 +2066,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -2059,19 +2074,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="8" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="C38" s="8" t="s">
+      <x:c r="D38" s="8" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D38" s="8" t="s">
+      <x:c r="E38" s="3" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="E38" s="3" t="s">
+      <x:c r="F38" s="3" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="F38" s="3" t="s">
-        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -2188,7 +2203,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="E44" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F44" s="3" t="s">
         <x:v>188</x:v>
@@ -2251,7 +2266,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="F47" s="3" t="s">
-        <x:v>198</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -2259,19 +2274,19 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B48" s="8" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D48" s="8" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="E48" s="3" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F48" s="3" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="C48" s="8" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D48" s="8" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E48" s="3" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F48" s="3" t="s">
-        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -2291,7 +2306,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="F49" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -2299,19 +2314,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B50" s="8" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C50" s="8" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D50" s="8" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="E50" s="3" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F50" s="3" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="C50" s="8" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D50" s="8" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="E50" s="3" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F50" s="3" t="s">
-        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -2319,19 +2334,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B51" s="8" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D51" s="8" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F51" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -2339,19 +2354,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B52" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F52" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -2359,19 +2374,19 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B53" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D53" s="8" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F53" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -2379,19 +2394,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D54" s="8" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F54" s="3" t="s">
-        <x:v>220</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -2399,19 +2414,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B55" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C55" s="8" t="s">
-        <x:v>234</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D55" s="8" t="s">
-        <x:v>235</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E55" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="F55" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -2419,19 +2434,19 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B56" s="8" t="s">
-        <x:v>237</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>238</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D56" s="8" t="s">
-        <x:v>239</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E56" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F56" s="3" t="s">
-        <x:v>241</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -2439,19 +2454,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B57" s="8" t="s">
-        <x:v>242</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D57" s="8" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E57" s="3" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F57" s="3" t="s">
-        <x:v>246</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -2459,19 +2474,19 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B58" s="8" t="s">
-        <x:v>247</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D58" s="8" t="s">
-        <x:v>249</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E58" s="3" t="s">
-        <x:v>250</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F58" s="3" t="s">
-        <x:v>251</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -2479,19 +2494,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B59" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>253</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D59" s="8" t="s">
-        <x:v>254</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E59" s="3" t="s">
-        <x:v>255</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F59" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -2499,19 +2514,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B60" s="8" t="s">
-        <x:v>257</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
-        <x:v>258</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D60" s="8" t="s">
-        <x:v>259</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E60" s="3" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F60" s="3" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="F60" s="3" t="s">
-        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -2519,19 +2534,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B61" s="8" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D61" s="8" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E61" s="3" t="s">
-        <x:v>173</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F61" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -2539,19 +2554,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B62" s="8" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
-        <x:v>265</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D62" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E62" s="3" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F62" s="3" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -2559,19 +2574,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B63" s="8" t="s">
-        <x:v>269</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C63" s="8" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D63" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E63" s="3" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F63" s="3" t="s">
-        <x:v>273</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -2579,19 +2594,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B64" s="8" t="s">
-        <x:v>274</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
-        <x:v>275</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D64" s="8" t="s">
-        <x:v>276</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E64" s="3" t="s">
-        <x:v>277</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F64" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -2599,19 +2614,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B65" s="8" t="s">
-        <x:v>279</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>280</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D65" s="8" t="s">
-        <x:v>281</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E65" s="3" t="s">
-        <x:v>282</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F65" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -2619,19 +2634,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B66" s="8" t="s">
-        <x:v>283</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>284</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D66" s="8" t="s">
-        <x:v>285</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E66" s="3" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F66" s="3" t="s">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -2639,19 +2654,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B67" s="8" t="s">
-        <x:v>288</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>289</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D67" s="8" t="s">
-        <x:v>290</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E67" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="F67" s="3" t="s">
-        <x:v>291</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -2667,16 +2682,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B69" s="5" t="s">
-        <x:v>292</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C69" s="5" t="s">
-        <x:v>293</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D69" s="6" t="s">
-        <x:v>294</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E69" s="6" t="s">
-        <x:v>295</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F69" s="6" t="s">
         <x:v>15</x:v>
@@ -2687,19 +2702,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B70" s="8" t="s">
-        <x:v>296</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>297</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D70" s="3" t="s">
-        <x:v>298</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E70" s="3" t="s">
-        <x:v>299</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F70" s="3" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -2712,19 +2727,19 @@
     </x:row>
     <x:row r="72" spans="1:6">
       <x:c r="A72" s="4" t="s">
-        <x:v>301</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B72" s="4" t="s">
-        <x:v>302</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C72" s="5" t="s">
-        <x:v>303</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D72" s="6" t="s">
-        <x:v>294</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E72" s="4" t="s">
-        <x:v>295</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F72" s="6" t="s">
         <x:v>15</x:v>
@@ -2732,42 +2747,42 @@
     </x:row>
     <x:row r="73" spans="1:6">
       <x:c r="A73" s="7" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B73" s="7" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C73" s="8" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D73" s="3" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="B73" s="7" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="C73" s="8" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D73" s="3" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E73" s="7" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="F73" s="3" t="s">
-        <x:v>309</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
       <x:c r="A74" s="7" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B74" s="7" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B74" s="7" t="s">
-        <x:v>305</x:v>
-      </x:c>
       <x:c r="C74" s="8" t="s">
-        <x:v>311</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D74" s="3" t="s">
-        <x:v>312</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E74" s="7" t="s">
-        <x:v>308</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F74" s="3" t="s">
-        <x:v>313</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -2780,13 +2795,13 @@
     </x:row>
     <x:row r="76" spans="1:6">
       <x:c r="A76" s="5" t="s">
-        <x:v>314</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B76" s="5" t="s">
-        <x:v>315</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C76" s="6" t="s">
-        <x:v>316</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D76" s="6" t="s">
         <x:v>15</x:v>
@@ -2794,44 +2809,44 @@
     </x:row>
     <x:row r="77" spans="1:6">
       <x:c r="A77" s="8" t="s">
-        <x:v>317</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B77" s="8" t="s">
-        <x:v>318</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C77" s="3" t="s">
-        <x:v>319</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="D77" s="3" t="s">
-        <x:v>320</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
       <x:c r="A78" s="8" t="s">
-        <x:v>321</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B78" s="8" t="s">
-        <x:v>318</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C78" s="3" t="s">
-        <x:v>322</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D78" s="3" t="s">
-        <x:v>323</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
       <x:c r="A79" s="8" t="s">
-        <x:v>324</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B79" s="8" t="s">
-        <x:v>318</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C79" s="3" t="s">
-        <x:v>325</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D79" s="3" t="s">
-        <x:v>326</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
